--- a/quizzes/peinture-20e-niveau2.xlsx
+++ b/quizzes/peinture-20e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D57AE93F-9305-485F-9DE9-ECC69CB707D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEE4D42-4EFD-441A-99E7-E3F81FD9D5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,9 +280,6 @@
     <t>Composition II en rouge, bleu et jaune</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Kazimir_Malevich%2C_1915%2C_Black_Suprematic_Square%2C_oil_on_linen_canvas%2C_79.5_x_79.5_cm%2C_Tretyakov_Gallery%2C_Moscow.jpg/1280px-Kazimir_Malevich%2C_1915%2C_Black_Suprematic_Square%2C_oil_on_linen_canvas%2C_79.5_x_79.5_cm%2C_Tretyakov_Gallery%2C_Moscow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Kazimir MALEVICH</t>
   </si>
   <si>
@@ -799,9 +796,6 @@
     <t>Francisco d'Andrade dans le rôle de Don Giovanni</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e3/Enlevement_des_filles_de_Leucippe-Ker-Xavier_Roussel-IMG_8198.JPG/1280px-Enlevement_des_filles_de_Leucippe-Ker-Xavier_Roussel-IMG_8198.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Ker-Xavier ROUSSEL</t>
   </si>
   <si>
@@ -818,6 +812,12 @@
   </si>
   <si>
     <t>Costume pour L'Après-midi d'un faune</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG/960px-Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -1270,1086 +1270,1089 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>209</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>212</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>39</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>242</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>243</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>42</v>
+        <v>244</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>44</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>197</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>52</v>
+        <v>198</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>53</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>207</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>110</v>
+        <v>205</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>111</v>
+        <v>198</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>113</v>
+        <v>218</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>61</v>
+        <v>220</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>116</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>140</v>
+      <c r="A29" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="7">
-        <v>1952</v>
+        <v>143</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="4" t="s">
-        <v>143</v>
+      <c r="A32" s="6" t="s">
+        <v>264</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="4" t="s">
-        <v>148</v>
+      <c r="A33" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>149</v>
+        <v>258</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>151</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="4" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>157</v>
+        <v>261</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>154</v>
+        <v>262</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>159</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>162</v>
+        <v>226</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>165</v>
+        <v>251</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>167</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>181</v>
+        <v>11</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>183</v>
+        <v>13</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>184</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>185</v>
+        <v>238</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>183</v>
+        <v>93</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="4" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>52</v>
+        <v>256</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>194</v>
+        <v>7</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="4" t="s">
-        <v>197</v>
+      <c r="A45" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>88</v>
+        <v>129</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1952</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="4" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>12</v>
+        <v>235</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>94</v>
+        <v>236</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="4" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="4" t="s">
-        <v>219</v>
+        <v>67</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>220</v>
+        <v>68</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>221</v>
+        <v>69</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>222</v>
+        <v>70</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>223</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
-        <v>224</v>
+        <v>72</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>225</v>
+        <v>73</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>227</v>
+        <v>43</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>228</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="4" t="s">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>233</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>235</v>
+        <v>41</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>236</v>
+        <v>42</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>237</v>
+        <v>43</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>238</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>239</v>
+        <v>107</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>242</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>246</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>250</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
-        <v>251</v>
+        <v>95</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>252</v>
+        <v>96</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>253</v>
+        <v>52</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>254</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="4" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>257</v>
+        <v>198</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="4" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>261</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="4" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>263</v>
+        <v>51</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>264</v>
+        <v>52</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>265</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E61">
+    <sortCondition ref="B2:B61"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="A30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="A31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A29" r:id="rId30" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{7C98424D-B0BE-4286-99EC-083D7C83EFB6}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{FEC8FA9B-D46E-4965-BCD5-AC9BA2CA4C36}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{81DEAAC0-B74C-4EBF-9F41-3F63DB7CC71F}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{22B3E07D-D3D0-4A0B-8436-D64A0CC8846C}"/>
-    <hyperlink ref="A36" r:id="rId35" xr:uid="{C5D0075F-FD6A-44AC-A8BF-A2DA5E797D6B}"/>
-    <hyperlink ref="A37" r:id="rId36" xr:uid="{36739142-CC5C-4963-AAE7-4EFF5DD1FF69}"/>
-    <hyperlink ref="A38" r:id="rId37" xr:uid="{BB1F07F8-AEF8-4D4F-8699-055D80226940}"/>
-    <hyperlink ref="A39" r:id="rId38" xr:uid="{742301CC-340B-41DB-AABE-DD82B7BEED6C}"/>
-    <hyperlink ref="A40" r:id="rId39" xr:uid="{4793370A-CA5E-4DB4-A9B6-8D2DE4C0A144}"/>
-    <hyperlink ref="A41" r:id="rId40" xr:uid="{B64362C5-9219-49FD-B4CB-2A210E23E202}"/>
-    <hyperlink ref="A42" r:id="rId41" xr:uid="{E6BD8294-7DF4-419D-8337-429DB2505386}"/>
-    <hyperlink ref="A43" r:id="rId42" xr:uid="{9BE6C77B-423D-4B0C-8748-8E9E43CE535C}"/>
-    <hyperlink ref="A44" r:id="rId43" xr:uid="{2D44F73D-C474-4008-A468-B26D37CC8269}"/>
-    <hyperlink ref="A45" r:id="rId44" xr:uid="{3A7EDFC1-A143-4B05-A2C1-37416316A162}"/>
-    <hyperlink ref="A46" r:id="rId45" xr:uid="{1DBE42F5-021D-47B1-82F9-CF2CDBA64228}"/>
-    <hyperlink ref="A47" r:id="rId46" xr:uid="{209900AF-FF8A-4ABF-8DC7-FFA0ADA48DBC}"/>
-    <hyperlink ref="A48" r:id="rId47" xr:uid="{43693F04-116C-4B24-9B94-650AAFA3610D}"/>
-    <hyperlink ref="A49" r:id="rId48" xr:uid="{3788085D-17B8-4B4A-B3DF-C53247D6A97F}"/>
-    <hyperlink ref="A50" r:id="rId49" xr:uid="{8EF6FCEB-993A-41A8-8068-9BAC6BF627CB}"/>
-    <hyperlink ref="A51" r:id="rId50" xr:uid="{43E0740A-9068-43A3-BF37-E6A053F906A8}"/>
-    <hyperlink ref="A52" r:id="rId51" xr:uid="{68998D0E-BB71-44BC-ADCD-603BF043BDBA}"/>
-    <hyperlink ref="A53" r:id="rId52" xr:uid="{CADE0A3D-564D-40B7-895D-E405B704297D}"/>
-    <hyperlink ref="A54" r:id="rId53" xr:uid="{B8CACDF2-680A-48D0-B966-5DD36D59603A}"/>
-    <hyperlink ref="A55" r:id="rId54" xr:uid="{6C8DD568-38DD-416D-98FE-AAB8899B5E5D}"/>
-    <hyperlink ref="A56" r:id="rId55" xr:uid="{6C0FBF95-A247-47B9-B7B7-DCA142C38859}"/>
-    <hyperlink ref="A57" r:id="rId56" xr:uid="{75965316-2276-48A7-AFFA-91A687C410CF}"/>
-    <hyperlink ref="A58" r:id="rId57" xr:uid="{2A4F4B62-ED9F-41EC-8FEF-360F10A64BAF}"/>
-    <hyperlink ref="A59" r:id="rId58" xr:uid="{450F046E-1772-442D-BA22-F9110DF8E152}"/>
-    <hyperlink ref="A60" r:id="rId59" xr:uid="{D19848FC-96BE-410E-9500-E081CAF863F2}"/>
-    <hyperlink ref="A61" r:id="rId60" xr:uid="{DAC13AAE-150A-488D-9A16-FE816F3BB5B8}"/>
+    <hyperlink ref="A10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A26" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A23" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A60" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A54" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A17" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A61" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A4" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A27" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A51" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A52" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A40" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A53" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="A18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A58" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A7" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A55" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="A30" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="A34" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="A21" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="A22" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="A16" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="A28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="A45" r:id="rId29" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
+    <hyperlink ref="A29" r:id="rId30" xr:uid="{7C98424D-B0BE-4286-99EC-083D7C83EFB6}"/>
+    <hyperlink ref="A56" r:id="rId31" xr:uid="{FEC8FA9B-D46E-4965-BCD5-AC9BA2CA4C36}"/>
+    <hyperlink ref="A39" r:id="rId32" xr:uid="{81DEAAC0-B74C-4EBF-9F41-3F63DB7CC71F}"/>
+    <hyperlink ref="A6" r:id="rId33" xr:uid="{22B3E07D-D3D0-4A0B-8436-D64A0CC8846C}"/>
+    <hyperlink ref="A19" r:id="rId34" xr:uid="{C5D0075F-FD6A-44AC-A8BF-A2DA5E797D6B}"/>
+    <hyperlink ref="A44" r:id="rId35" xr:uid="{36739142-CC5C-4963-AAE7-4EFF5DD1FF69}"/>
+    <hyperlink ref="A31" r:id="rId36" xr:uid="{BB1F07F8-AEF8-4D4F-8699-055D80226940}"/>
+    <hyperlink ref="A3" r:id="rId37" xr:uid="{742301CC-340B-41DB-AABE-DD82B7BEED6C}"/>
+    <hyperlink ref="A38" r:id="rId38" xr:uid="{4793370A-CA5E-4DB4-A9B6-8D2DE4C0A144}"/>
+    <hyperlink ref="A15" r:id="rId39" xr:uid="{B64362C5-9219-49FD-B4CB-2A210E23E202}"/>
+    <hyperlink ref="A8" r:id="rId40" xr:uid="{E6BD8294-7DF4-419D-8337-429DB2505386}"/>
+    <hyperlink ref="A57" r:id="rId41" xr:uid="{9BE6C77B-423D-4B0C-8748-8E9E43CE535C}"/>
+    <hyperlink ref="A50" r:id="rId42" xr:uid="{2D44F73D-C474-4008-A468-B26D37CC8269}"/>
+    <hyperlink ref="A11" r:id="rId43" xr:uid="{3A7EDFC1-A143-4B05-A2C1-37416316A162}"/>
+    <hyperlink ref="A59" r:id="rId44" xr:uid="{1DBE42F5-021D-47B1-82F9-CF2CDBA64228}"/>
+    <hyperlink ref="A24" r:id="rId45" xr:uid="{209900AF-FF8A-4ABF-8DC7-FFA0ADA48DBC}"/>
+    <hyperlink ref="A12" r:id="rId46" xr:uid="{43693F04-116C-4B24-9B94-650AAFA3610D}"/>
+    <hyperlink ref="A2" r:id="rId47" xr:uid="{3788085D-17B8-4B4A-B3DF-C53247D6A97F}"/>
+    <hyperlink ref="A47" r:id="rId48" xr:uid="{8EF6FCEB-993A-41A8-8068-9BAC6BF627CB}"/>
+    <hyperlink ref="A25" r:id="rId49" xr:uid="{43E0740A-9068-43A3-BF37-E6A053F906A8}"/>
+    <hyperlink ref="A36" r:id="rId50" xr:uid="{68998D0E-BB71-44BC-ADCD-603BF043BDBA}"/>
+    <hyperlink ref="A49" r:id="rId51" xr:uid="{CADE0A3D-564D-40B7-895D-E405B704297D}"/>
+    <hyperlink ref="A48" r:id="rId52" xr:uid="{B8CACDF2-680A-48D0-B966-5DD36D59603A}"/>
+    <hyperlink ref="A42" r:id="rId53" xr:uid="{6C8DD568-38DD-416D-98FE-AAB8899B5E5D}"/>
+    <hyperlink ref="A9" r:id="rId54" xr:uid="{6C0FBF95-A247-47B9-B7B7-DCA142C38859}"/>
+    <hyperlink ref="A46" r:id="rId55" xr:uid="{75965316-2276-48A7-AFFA-91A687C410CF}"/>
+    <hyperlink ref="A37" r:id="rId56" xr:uid="{2A4F4B62-ED9F-41EC-8FEF-360F10A64BAF}"/>
+    <hyperlink ref="A43" r:id="rId57" xr:uid="{450F046E-1772-442D-BA22-F9110DF8E152}"/>
+    <hyperlink ref="A35" r:id="rId58" xr:uid="{DAC13AAE-150A-488D-9A16-FE816F3BB5B8}"/>
+    <hyperlink ref="A32" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{69E67874-C0ED-43E7-857A-B28604B5FAFA}"/>
+    <hyperlink ref="A33" r:id="rId60" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG/960px-Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9C030EC2-1422-48F9-B330-74E775316386}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-20e-niveau2.xlsx
+++ b/quizzes/peinture-20e-niveau2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEE4D42-4EFD-441A-99E7-E3F81FD9D5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BEA792-B516-46D9-BCAA-15B40493C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="765" windowWidth="15735" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz peinture 20e niveau1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="265">
   <si>
     <t>image</t>
   </si>
@@ -37,9 +37,6 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2c/Ch%C3%AF%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg/1280px-Ch%C3%AF%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Chaïm SOUTINE</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>Le Bœuf écorché</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/44/Self-Portrait_in_Tuxedo.jpg/1280px-Self-Portrait_in_Tuxedo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Max BECKMANN</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>Autoportrait en smoking</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/16/Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg/1280px-Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>André DERAIN</t>
   </si>
   <si>
@@ -82,9 +73,6 @@
     <t>Le Pont de Charing Cross</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/La_Danse_II%2C_par_Henri_Matisse.jpg/1280px-La_Danse_II%2C_par_Henri_Matisse.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Henri MATISSE</t>
   </si>
   <si>
@@ -112,9 +100,6 @@
     <t>Le Baiser</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/1280px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Edvard MUNCH</t>
   </si>
   <si>
@@ -127,9 +112,6 @@
     <t>Le Cri (version de 1910)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Kandinsky_-_Composition_8%2C_July_1923.jpg/1280px-Kandinsky_-_Composition_8%2C_July_1923.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Wassily KANDINSKY</t>
   </si>
   <si>
@@ -142,9 +124,6 @@
     <t>Composition 8</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8a/Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg/1280px-Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Raoul DUFY</t>
   </si>
   <si>
@@ -157,9 +136,6 @@
     <t>La Fée Électricité</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Ferdinand_hodler%2C_lo_jungfrau_tra_la_nebbia%2C_1908.JPG/1280px-Ferdinand_hodler%2C_lo_jungfrau_tra_la_nebbia%2C_1908.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Ferdinand HODLER</t>
   </si>
   <si>
@@ -172,9 +148,6 @@
     <t>La Jungfrau dans le brouillard</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Mama%2C_Papa_is_Wounded%21.jpg/1280px-Mama%2C_Papa_is_Wounded%21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Yves TANGUY</t>
   </si>
   <si>
@@ -184,9 +157,6 @@
     <t>Maman, Papa est blessé !</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Modigliani_-_Nu_couch%C3%A9.jpg/1280px-Modigliani_-_Nu_couch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Amedeo MODIGLIANI</t>
   </si>
   <si>
@@ -199,9 +169,6 @@
     <t>Nu couché</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Egon SCHIELE</t>
   </si>
   <si>
@@ -214,18 +181,12 @@
     <t>Autoportrait à la tête baissée</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg/1280px-Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Henri ROUSSEAU (Le Douanier)</t>
   </si>
   <si>
     <t>Le Rêve</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/64/Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg/1280px-Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Pavel FILONOV</t>
   </si>
   <si>
@@ -238,9 +199,6 @@
     <t>Formule du prolétariat de Petrograd</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg/1280px-Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Pierre BONNARD</t>
   </si>
   <si>
@@ -265,9 +223,6 @@
     <t>La Maison de Berlioz (Montmartre)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Piet MONDRIAN</t>
   </si>
   <si>
@@ -292,33 +247,18 @@
     <t>Carré noir sur fond blanc</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d0/Composition_au_damier_-_Fernand_L%C3%A9ger.jpg/1280px-Composition_au_damier_-_Fernand_L%C3%A9ger.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Fernand LÉGER</t>
   </si>
   <si>
-    <t>1929</t>
-  </si>
-  <si>
     <t>Collection privée</t>
   </si>
   <si>
-    <t>Composition au damier</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/The_City_Rises_by_Umberto_Boccioni_1910.jpg/1280px-The_City_Rises_by_Umberto_Boccioni_1910.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Umberto BOCCIONI</t>
   </si>
   <si>
     <t>La Ville qui monte</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2b/Franz_Marc_-_Die_gro%C3%9Fen_blauen_Pferde_1911.jpg/1280px-Franz_Marc_-_Die_gro%C3%9Fen_blauen_Pferde_1911.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Franz MARC</t>
   </si>
   <si>
@@ -331,21 +271,9 @@
     <t>Les Grands Chevaux bleus</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg/1280px-August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>August MACKE</t>
   </si>
   <si>
-    <t>Museum Ludwig, Cologne</t>
-  </si>
-  <si>
-    <t>Marché de Tunis II</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/85/Robert_delaunay%2C_tour_eiffel%2C_1926.jpg/1280px-Robert_delaunay%2C_tour_eiffel%2C_1926.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Robert DELAUNAY</t>
   </si>
   <si>
@@ -358,9 +286,6 @@
     <t>La Tour Eiffel</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6f/Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg/1280px-Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Juan GRIS</t>
   </si>
   <si>
@@ -370,9 +295,6 @@
     <t>Portrait de Pablo Picasso</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG/1280px-Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>László MOHOLY-NAGY</t>
   </si>
   <si>
@@ -385,9 +307,6 @@
     <t>Composition A.XX</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/The_Two_Fridas.jpg/1280px-The_Two_Fridas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Frida KAHLO</t>
   </si>
   <si>
@@ -400,9 +319,6 @@
     <t>Les Deux Frida</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Grant_Wood_-_American_Gothic_%281930%29.jpg/1280px-Grant_Wood_-_American_Gothic_%281930%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Grant WOOD</t>
   </si>
   <si>
@@ -538,9 +454,6 @@
     <t>Jeune fille nue endormie</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Alexej_von_Jawlensky_-_Mystischer_Kopf.jpg/1280px-Alexej_von_Jawlensky_-_Mystischer_Kopf.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Alexej von JAWLENSKY</t>
   </si>
   <si>
@@ -818,6 +731,90 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG/960px-Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg/1280px-L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Mama%2C_Papa_is_Wounded%21.jpg/960px-Mama%2C_Papa_is_Wounded%21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Grant_Wood_-_American_Gothic_%281930%29.jpg/960px-Grant_Wood_-_American_Gothic_%281930%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Franz_Marc_005.jpg/1280px-Franz_Marc_005.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/960px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b5/Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg/1280px-Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Jeunes filles sous les arbres</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG/960px-Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Alexej_von_Jawlensky_-_Mystischer_Kopf_%281917%29.jpg/960px-Alexej_von_Jawlensky_-_Mystischer_Kopf_%281917%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Modigliani_-_Nu_couch%C3%A9.jpg/1280px-Modigliani_-_Nu_couch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Cha%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg/1280px-Cha%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg/1920px-Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Centre national d’art et de culture Georges-Pompidou du Paris </t>
+  </si>
+  <si>
+    <t>Le Mécanicien</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Les_Deux_Fridas.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8a/La_Danse_II%2C_par_Henri_Matisse.jpg/1280px-La_Danse_II%2C_par_Henri_Matisse.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg/1280px-Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg/1280px-Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Self-Portrait_in_Tuxedo.jpg/1280px-Self-Portrait_in_Tuxedo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3d/Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg/1280px-Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg/1280px-Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg/1280px-Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/Robert_delaunay%2C_tour_eiffel%2C_1926.jpg/1280px-Robert_delaunay%2C_tour_eiffel%2C_1926.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b4/The_City_Rises_by_Umberto_Boccioni_1910.jpg/1280px-The_City_Rises_by_Umberto_Boccioni_1910.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Kandinsky_-_Composition_8%2C_July_1923.jpg/1280px-Kandinsky_-_Composition_8%2C_July_1923.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
 </sst>
 </file>
@@ -1270,1022 +1267,1022 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>212</v>
+        <v>183</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>172</v>
+      <c r="A3" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
-        <v>54</v>
+      <c r="A4" s="6" t="s">
+        <v>247</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>103</v>
+        <v>243</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>105</v>
+        <v>227</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>106</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>30</v>
+      <c r="A13" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
-        <v>45</v>
+      <c r="A17" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
-        <v>90</v>
+      <c r="A18" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1918</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>93</v>
+        <v>252</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>94</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="5" t="s">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>257</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="4" t="s">
-        <v>116</v>
+      <c r="A34" s="6" t="s">
+        <v>245</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="4" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="C45" s="7">
         <v>1952</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="4" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="4" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="4" t="s">
-        <v>67</v>
+        <v>259</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="4" t="s">
-        <v>81</v>
+      <c r="A53" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>40</v>
+        <v>261</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>107</v>
+        <v>262</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
-        <v>95</v>
+        <v>263</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="4" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="14.25" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>35</v>
+        <v>264</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="4" t="s">
-        <v>50</v>
+      <c r="A61" s="6" t="s">
+        <v>239</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2293,66 +2290,66 @@
     <sortCondition ref="B2:B61"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A26" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A23" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="A60" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="A54" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A17" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="A61" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="A4" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A27" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="A51" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="A52" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A40" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A53" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="A18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="A58" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A7" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="A55" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="A30" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A34" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="A21" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="A22" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="A16" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="A28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A45" r:id="rId29" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
-    <hyperlink ref="A29" r:id="rId30" xr:uid="{7C98424D-B0BE-4286-99EC-083D7C83EFB6}"/>
-    <hyperlink ref="A56" r:id="rId31" xr:uid="{FEC8FA9B-D46E-4965-BCD5-AC9BA2CA4C36}"/>
-    <hyperlink ref="A39" r:id="rId32" xr:uid="{81DEAAC0-B74C-4EBF-9F41-3F63DB7CC71F}"/>
-    <hyperlink ref="A6" r:id="rId33" xr:uid="{22B3E07D-D3D0-4A0B-8436-D64A0CC8846C}"/>
-    <hyperlink ref="A19" r:id="rId34" xr:uid="{C5D0075F-FD6A-44AC-A8BF-A2DA5E797D6B}"/>
-    <hyperlink ref="A44" r:id="rId35" xr:uid="{36739142-CC5C-4963-AAE7-4EFF5DD1FF69}"/>
-    <hyperlink ref="A31" r:id="rId36" xr:uid="{BB1F07F8-AEF8-4D4F-8699-055D80226940}"/>
-    <hyperlink ref="A3" r:id="rId37" xr:uid="{742301CC-340B-41DB-AABE-DD82B7BEED6C}"/>
-    <hyperlink ref="A38" r:id="rId38" xr:uid="{4793370A-CA5E-4DB4-A9B6-8D2DE4C0A144}"/>
-    <hyperlink ref="A15" r:id="rId39" xr:uid="{B64362C5-9219-49FD-B4CB-2A210E23E202}"/>
-    <hyperlink ref="A8" r:id="rId40" xr:uid="{E6BD8294-7DF4-419D-8337-429DB2505386}"/>
-    <hyperlink ref="A57" r:id="rId41" xr:uid="{9BE6C77B-423D-4B0C-8748-8E9E43CE535C}"/>
-    <hyperlink ref="A50" r:id="rId42" xr:uid="{2D44F73D-C474-4008-A468-B26D37CC8269}"/>
-    <hyperlink ref="A11" r:id="rId43" xr:uid="{3A7EDFC1-A143-4B05-A2C1-37416316A162}"/>
-    <hyperlink ref="A59" r:id="rId44" xr:uid="{1DBE42F5-021D-47B1-82F9-CF2CDBA64228}"/>
-    <hyperlink ref="A24" r:id="rId45" xr:uid="{209900AF-FF8A-4ABF-8DC7-FFA0ADA48DBC}"/>
-    <hyperlink ref="A12" r:id="rId46" xr:uid="{43693F04-116C-4B24-9B94-650AAFA3610D}"/>
-    <hyperlink ref="A2" r:id="rId47" xr:uid="{3788085D-17B8-4B4A-B3DF-C53247D6A97F}"/>
-    <hyperlink ref="A47" r:id="rId48" xr:uid="{8EF6FCEB-993A-41A8-8068-9BAC6BF627CB}"/>
-    <hyperlink ref="A25" r:id="rId49" xr:uid="{43E0740A-9068-43A3-BF37-E6A053F906A8}"/>
-    <hyperlink ref="A36" r:id="rId50" xr:uid="{68998D0E-BB71-44BC-ADCD-603BF043BDBA}"/>
-    <hyperlink ref="A49" r:id="rId51" xr:uid="{CADE0A3D-564D-40B7-895D-E405B704297D}"/>
-    <hyperlink ref="A48" r:id="rId52" xr:uid="{B8CACDF2-680A-48D0-B966-5DD36D59603A}"/>
-    <hyperlink ref="A42" r:id="rId53" xr:uid="{6C8DD568-38DD-416D-98FE-AAB8899B5E5D}"/>
-    <hyperlink ref="A9" r:id="rId54" xr:uid="{6C0FBF95-A247-47B9-B7B7-DCA142C38859}"/>
-    <hyperlink ref="A46" r:id="rId55" xr:uid="{75965316-2276-48A7-AFFA-91A687C410CF}"/>
-    <hyperlink ref="A37" r:id="rId56" xr:uid="{2A4F4B62-ED9F-41EC-8FEF-360F10A64BAF}"/>
-    <hyperlink ref="A43" r:id="rId57" xr:uid="{450F046E-1772-442D-BA22-F9110DF8E152}"/>
-    <hyperlink ref="A35" r:id="rId58" xr:uid="{DAC13AAE-150A-488D-9A16-FE816F3BB5B8}"/>
-    <hyperlink ref="A32" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{69E67874-C0ED-43E7-857A-B28604B5FAFA}"/>
-    <hyperlink ref="A33" r:id="rId60" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG/960px-Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9C030EC2-1422-48F9-B330-74E775316386}"/>
+    <hyperlink ref="A23" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A16" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="A28" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="A45" r:id="rId4" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
+    <hyperlink ref="A29" r:id="rId5" xr:uid="{7C98424D-B0BE-4286-99EC-083D7C83EFB6}"/>
+    <hyperlink ref="A56" r:id="rId6" xr:uid="{FEC8FA9B-D46E-4965-BCD5-AC9BA2CA4C36}"/>
+    <hyperlink ref="A39" r:id="rId7" xr:uid="{81DEAAC0-B74C-4EBF-9F41-3F63DB7CC71F}"/>
+    <hyperlink ref="A6" r:id="rId8" xr:uid="{22B3E07D-D3D0-4A0B-8436-D64A0CC8846C}"/>
+    <hyperlink ref="A19" r:id="rId9" xr:uid="{C5D0075F-FD6A-44AC-A8BF-A2DA5E797D6B}"/>
+    <hyperlink ref="A44" r:id="rId10" xr:uid="{36739142-CC5C-4963-AAE7-4EFF5DD1FF69}"/>
+    <hyperlink ref="A31" r:id="rId11" xr:uid="{BB1F07F8-AEF8-4D4F-8699-055D80226940}"/>
+    <hyperlink ref="A38" r:id="rId12" xr:uid="{4793370A-CA5E-4DB4-A9B6-8D2DE4C0A144}"/>
+    <hyperlink ref="A15" r:id="rId13" xr:uid="{B64362C5-9219-49FD-B4CB-2A210E23E202}"/>
+    <hyperlink ref="A8" r:id="rId14" xr:uid="{E6BD8294-7DF4-419D-8337-429DB2505386}"/>
+    <hyperlink ref="A57" r:id="rId15" xr:uid="{9BE6C77B-423D-4B0C-8748-8E9E43CE535C}"/>
+    <hyperlink ref="A50" r:id="rId16" xr:uid="{2D44F73D-C474-4008-A468-B26D37CC8269}"/>
+    <hyperlink ref="A11" r:id="rId17" xr:uid="{3A7EDFC1-A143-4B05-A2C1-37416316A162}"/>
+    <hyperlink ref="A59" r:id="rId18" xr:uid="{1DBE42F5-021D-47B1-82F9-CF2CDBA64228}"/>
+    <hyperlink ref="A24" r:id="rId19" xr:uid="{209900AF-FF8A-4ABF-8DC7-FFA0ADA48DBC}"/>
+    <hyperlink ref="A12" r:id="rId20" xr:uid="{43693F04-116C-4B24-9B94-650AAFA3610D}"/>
+    <hyperlink ref="A2" r:id="rId21" xr:uid="{3788085D-17B8-4B4A-B3DF-C53247D6A97F}"/>
+    <hyperlink ref="A47" r:id="rId22" xr:uid="{8EF6FCEB-993A-41A8-8068-9BAC6BF627CB}"/>
+    <hyperlink ref="A25" r:id="rId23" xr:uid="{43E0740A-9068-43A3-BF37-E6A053F906A8}"/>
+    <hyperlink ref="A36" r:id="rId24" xr:uid="{68998D0E-BB71-44BC-ADCD-603BF043BDBA}"/>
+    <hyperlink ref="A49" r:id="rId25" xr:uid="{CADE0A3D-564D-40B7-895D-E405B704297D}"/>
+    <hyperlink ref="A48" r:id="rId26" xr:uid="{B8CACDF2-680A-48D0-B966-5DD36D59603A}"/>
+    <hyperlink ref="A42" r:id="rId27" xr:uid="{6C8DD568-38DD-416D-98FE-AAB8899B5E5D}"/>
+    <hyperlink ref="A9" r:id="rId28" xr:uid="{6C0FBF95-A247-47B9-B7B7-DCA142C38859}"/>
+    <hyperlink ref="A46" r:id="rId29" xr:uid="{75965316-2276-48A7-AFFA-91A687C410CF}"/>
+    <hyperlink ref="A37" r:id="rId30" xr:uid="{2A4F4B62-ED9F-41EC-8FEF-360F10A64BAF}"/>
+    <hyperlink ref="A43" r:id="rId31" xr:uid="{450F046E-1772-442D-BA22-F9110DF8E152}"/>
+    <hyperlink ref="A35" r:id="rId32" xr:uid="{DAC13AAE-150A-488D-9A16-FE816F3BB5B8}"/>
+    <hyperlink ref="A32" r:id="rId33" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{69E67874-C0ED-43E7-857A-B28604B5FAFA}"/>
+    <hyperlink ref="A33" r:id="rId34" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG/960px-Ker-xavier_roussel%2C_il_rapimento_delle_figlie_di_leucippe%2C_1911%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9C030EC2-1422-48F9-B330-74E775316386}"/>
+    <hyperlink ref="A53" r:id="rId35" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C94EBE83-657A-40D5-B0CD-E1F00D869815}"/>
+    <hyperlink ref="A17" r:id="rId36" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg/1280px-L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4F1A15E3-4E79-4BF4-A329-68843D524B24}"/>
+    <hyperlink ref="A61" r:id="rId37" xr:uid="{2078EEAB-2A97-4A3C-AA73-25CC8F4A60F0}"/>
+    <hyperlink ref="A22" r:id="rId38" xr:uid="{9994A922-AF8B-45A9-8232-F7C7C4927CE1}"/>
+    <hyperlink ref="A20" r:id="rId39" xr:uid="{1D572155-16A2-474A-A7C5-82A5B4F54B24}"/>
+    <hyperlink ref="A13" r:id="rId40" xr:uid="{34199626-6F7A-4433-B859-92FF7FF802C6}"/>
+    <hyperlink ref="A34" r:id="rId41" xr:uid="{77D9221F-0827-46A6-A23D-0EAB6177EF59}"/>
+    <hyperlink ref="A3" r:id="rId42" xr:uid="{77B826BB-1568-4C77-812D-3B98D41B9C8A}"/>
+    <hyperlink ref="A4" r:id="rId43" xr:uid="{D3E9FE59-BA13-44A5-A884-F7E50358A4FC}"/>
+    <hyperlink ref="A5" r:id="rId44" xr:uid="{EB80C2A4-1767-426B-94EC-D4DD8C90CECD}"/>
+    <hyperlink ref="A7" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg/1280px-August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{C401B748-042F-4952-87B4-A315C61C394B}"/>
+    <hyperlink ref="A10" r:id="rId46" xr:uid="{205B2BE1-051A-4D01-8E04-8618B1EC7CBB}"/>
+    <hyperlink ref="A14" r:id="rId47" xr:uid="{16190D9C-3F1A-4FD6-806F-340FADCB9383}"/>
+    <hyperlink ref="A18" r:id="rId48" xr:uid="{B4A063C7-FCF4-4594-A0EF-0DF178D9FB67}"/>
+    <hyperlink ref="A21" r:id="rId49" xr:uid="{D744EE2D-C7FC-42D5-A088-56A8A752398A}"/>
+    <hyperlink ref="A26" r:id="rId50" xr:uid="{9265BFAE-BD45-40D6-964B-5479293F82B7}"/>
+    <hyperlink ref="A27" r:id="rId51" xr:uid="{99F34991-56F4-4DBF-9832-D81EE883D626}"/>
+    <hyperlink ref="A30" r:id="rId52" xr:uid="{5D04CF0B-3ACA-4BD8-94AE-DA3BE2D96690}"/>
+    <hyperlink ref="A40" r:id="rId53" xr:uid="{93B6D60B-7CD1-4BF5-A0DD-6AB096B0B941}"/>
+    <hyperlink ref="A41" r:id="rId54" xr:uid="{9537EB73-6A9B-47DF-B76C-13B3DC5BD44D}"/>
+    <hyperlink ref="A51" r:id="rId55" xr:uid="{4B3AEE58-26CD-47E5-9E01-AABDD509DE79}"/>
+    <hyperlink ref="A52" r:id="rId56" xr:uid="{9860B263-0687-4E11-AB45-FC096E7989CB}"/>
+    <hyperlink ref="A54" r:id="rId57" xr:uid="{3ED8D9D2-79E0-4F4D-BB27-6BE13B0F567E}"/>
+    <hyperlink ref="A55" r:id="rId58" xr:uid="{3512D829-A954-4D58-A952-476B493B48A4}"/>
+    <hyperlink ref="A58" r:id="rId59" xr:uid="{AA5F02BD-6203-4C29-B804-A72206B93E68}"/>
+    <hyperlink ref="A60" r:id="rId60" xr:uid="{49A69B40-C96B-454D-85F4-79447702B569}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-20e-niveau2.xlsx
+++ b/quizzes/peinture-20e-niveau2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BEA792-B516-46D9-BCAA-15B40493C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B30091-192F-458F-8AF8-F5AC406F1FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="765" windowWidth="15735" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz peinture 20e niveau1" sheetId="1" r:id="rId1"/>
@@ -208,9 +208,6 @@
     <t>Nu dans le bain</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg/1280px-Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Maurice UTRILLO</t>
   </si>
   <si>
@@ -815,6 +812,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Kandinsky_-_Composition_8%2C_July_1923.jpg/1280px-Kandinsky_-_Composition_8%2C_July_1923.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg/1280px-Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
 </sst>
 </file>
@@ -1267,41 +1267,41 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>45</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>13</v>
@@ -1335,75 +1335,75 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>5</v>
@@ -1420,41 +1420,41 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>26</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>49</v>
@@ -1488,41 +1488,41 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>38</v>
@@ -1539,87 +1539,87 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" s="7">
         <v>1918</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1641,41 +1641,41 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>17</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>53</v>
@@ -1709,228 +1709,228 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>232</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
@@ -1947,160 +1947,160 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C45" s="7">
         <v>1952</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>55</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>59</v>
@@ -2134,24 +2134,24 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>34</v>
@@ -2168,61 +2168,61 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D56" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>27</v>
@@ -2231,29 +2231,29 @@
         <v>43</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="14.25" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>30</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>42</v>
@@ -2342,14 +2342,14 @@
     <hyperlink ref="A26" r:id="rId50" xr:uid="{9265BFAE-BD45-40D6-964B-5479293F82B7}"/>
     <hyperlink ref="A27" r:id="rId51" xr:uid="{99F34991-56F4-4DBF-9832-D81EE883D626}"/>
     <hyperlink ref="A30" r:id="rId52" xr:uid="{5D04CF0B-3ACA-4BD8-94AE-DA3BE2D96690}"/>
-    <hyperlink ref="A40" r:id="rId53" xr:uid="{93B6D60B-7CD1-4BF5-A0DD-6AB096B0B941}"/>
-    <hyperlink ref="A41" r:id="rId54" xr:uid="{9537EB73-6A9B-47DF-B76C-13B3DC5BD44D}"/>
-    <hyperlink ref="A51" r:id="rId55" xr:uid="{4B3AEE58-26CD-47E5-9E01-AABDD509DE79}"/>
-    <hyperlink ref="A52" r:id="rId56" xr:uid="{9860B263-0687-4E11-AB45-FC096E7989CB}"/>
-    <hyperlink ref="A54" r:id="rId57" xr:uid="{3ED8D9D2-79E0-4F4D-BB27-6BE13B0F567E}"/>
-    <hyperlink ref="A55" r:id="rId58" xr:uid="{3512D829-A954-4D58-A952-476B493B48A4}"/>
-    <hyperlink ref="A58" r:id="rId59" xr:uid="{AA5F02BD-6203-4C29-B804-A72206B93E68}"/>
-    <hyperlink ref="A60" r:id="rId60" xr:uid="{49A69B40-C96B-454D-85F4-79447702B569}"/>
+    <hyperlink ref="A41" r:id="rId53" xr:uid="{9537EB73-6A9B-47DF-B76C-13B3DC5BD44D}"/>
+    <hyperlink ref="A51" r:id="rId54" xr:uid="{4B3AEE58-26CD-47E5-9E01-AABDD509DE79}"/>
+    <hyperlink ref="A52" r:id="rId55" xr:uid="{9860B263-0687-4E11-AB45-FC096E7989CB}"/>
+    <hyperlink ref="A54" r:id="rId56" xr:uid="{3ED8D9D2-79E0-4F4D-BB27-6BE13B0F567E}"/>
+    <hyperlink ref="A55" r:id="rId57" xr:uid="{3512D829-A954-4D58-A952-476B493B48A4}"/>
+    <hyperlink ref="A58" r:id="rId58" xr:uid="{AA5F02BD-6203-4C29-B804-A72206B93E68}"/>
+    <hyperlink ref="A60" r:id="rId59" xr:uid="{49A69B40-C96B-454D-85F4-79447702B569}"/>
+    <hyperlink ref="A40" r:id="rId60" xr:uid="{E7E3F95B-AFDC-4A58-9847-3EEB96F476E9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-20e-niveau2.xlsx
+++ b/quizzes/peinture-20e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C0E96FC-281F-4FE5-8741-2C5926F327DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D57382F-0D10-47FF-9FB6-FC691F7DCDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="399">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2d/Notre_Dame_2_Albert_Marquet_%281904%29.jpg/1280px-Notre_Dame_2_Albert_Marquet_%281904%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>46 × 33 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Alexej_von_Jawlensky_-_Mystischer_Kopf_%281917%29.jpg/960px-Alexej_von_Jawlensky_-_Mystischer_Kopf_%281917%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>53,3 × 49,5 cm</t>
   </si>
   <si>
+    <t>russe</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Modigliani_-_Nu_couch%C3%A9.jpg/1280px-Modigliani_-_Nu_couch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -109,6 +118,9 @@
     <t>60 × 92 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -151,6 +163,9 @@
     <t>45,7 × 55,9 cm</t>
   </si>
   <si>
+    <t>américaine</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b5/Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg/1280px-Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -172,6 +187,9 @@
     <t>119,5 × 159,5 cm</t>
   </si>
   <si>
+    <t>allemande</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Kubista%2C_Bohumil_-_Kurak_%281907%29.jpg/1280px-Kubista%2C_Bohumil_-_Kurak_%281907%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -193,6 +211,9 @@
     <t>63,5 × 51,5 cm</t>
   </si>
   <si>
+    <t>tchèque</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d0/Woman_reading_by_Boris_Grigoriev_%28c.1922%2C_MetMuseum%29.jpg/1280px-Woman_reading_by_Boris_Grigoriev_%28c.1922%2C_MetMuseum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -232,6 +253,9 @@
     <t>202 × 114 cm</t>
   </si>
   <si>
+    <t>biélorusse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Christopher_richard_wynne_nevinson%2C_la_mitrailleuse%2C_1915.jpg/1280px-Christopher_richard_wynne_nevinson%2C_la_mitrailleuse%2C_1915.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -253,6 +277,9 @@
     <t>61 × 50,8 cm</t>
   </si>
   <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/Christopher_Wood_Autoportrait_1927.jpg/1280px-Christopher_Wood_Autoportrait_1927.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -295,6 +322,9 @@
     <t>91 × 73,5 cm</t>
   </si>
   <si>
+    <t>norvégienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -319,6 +349,9 @@
     <t>42,2 × 33,9 cm</t>
   </si>
   <si>
+    <t>autrichienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Filla_Emil%2C_Z%C3%A1ti%C5%A1%C3%AD_s_d%C3%BDmkou_%2C_1934.jpeg/1280px-Filla_Emil%2C_Z%C3%A1ti%C5%A1%C3%AD_s_d%C3%BDmkou_%2C_1934.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -376,6 +409,9 @@
     <t>environ 68 × 80 cm</t>
   </si>
   <si>
+    <t>suisse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg/1920px-Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -589,6 +625,9 @@
     <t>328 × 240 cm</t>
   </si>
   <si>
+    <t>suédoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/La_Calavera_Catrina_J_Guadalupe_Posada.jpg/1280px-La_Calavera_Catrina_J_Guadalupe_Posada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -610,6 +649,9 @@
     <t>Gravure sur zinc</t>
   </si>
   <si>
+    <t>mexicaine</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg/1280px-Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -625,6 +667,9 @@
     <t>93,4 × 74,3 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/JulesPascin-1928-Sleeping_Naked_Girl.png/1280px-JulesPascin-1928-Sleeping_Naked_Girl.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -643,6 +688,9 @@
     <t>1885-1930</t>
   </si>
   <si>
+    <t>bulgare</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -691,6 +739,9 @@
     <t>1895-1946</t>
   </si>
   <si>
+    <t>hongroise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d4/Bakst_Nizhinsky.jpg/1280px-Bakst_Nizhinsky.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -853,6 +904,9 @@
     <t>1891-1953</t>
   </si>
   <si>
+    <t>polonaise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5e/The_Football_Players.jpg/1280px-The_Football_Players.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
@@ -1016,6 +1070,9 @@
   </si>
   <si>
     <t>46 × 46 cm</t>
+  </si>
+  <si>
+    <t>hollandaise (Pays-Bas)</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg/1280px-Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -1608,1627 +1665,1749 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="1"/>
+        <v>99</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I16" s="1"/>
+        <v>121</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I17" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C18" s="7">
         <v>1918</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I18" s="1"/>
+        <v>135</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I19" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="1"/>
+        <v>148</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I21" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I22" s="1"/>
+        <v>162</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="I23" s="1"/>
+        <v>170</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="4" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I25" s="1"/>
+        <v>181</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I26" s="1"/>
+        <v>188</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="4" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I27" s="1"/>
+        <v>193</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I28" s="1"/>
+        <v>200</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="4" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I29" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="4" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I30" s="1"/>
+        <v>214</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I32" s="1"/>
+        <v>228</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I33" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I34" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I35" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="4" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="D37" s="5" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="I37" s="1"/>
+        <v>257</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="4" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="4" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="I39" s="1"/>
+        <v>268</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I40" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="4" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I41" s="1"/>
+        <v>279</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I42" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I43" s="1"/>
+        <v>288</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I44" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="6" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C45" s="7">
         <v>1952</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="I45" s="1"/>
+        <v>300</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I46" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I47" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I48" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="4" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="I49" s="1"/>
+        <v>324</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="4" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I50" s="1"/>
+        <v>330</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="4" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I51" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="4" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="I52" s="1"/>
+        <v>343</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="6" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="I53" s="1"/>
+        <v>349</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="4" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="I54" s="1"/>
+        <v>357</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="4" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I55" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="4" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="I56" s="1"/>
+        <v>371</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="4" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="I57" s="1"/>
+        <v>377</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="4" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="I58" s="1"/>
+        <v>382</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="4" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="I59" s="1"/>
+        <v>387</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="60" spans="1:9" ht="14.25" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="I60" s="1"/>
+        <v>393</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="6" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="I61" s="1"/>
+        <v>398</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
